--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488194_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488194_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.408200000000001</v>
+        <v>8.357799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.539</v>
+        <v>7.7349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8691</v>
+        <v>0.6229</v>
       </c>
       <c r="G2" t="n">
         <v>7.2282</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9936</v>
+        <v>0.9432</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6491</v>
+        <v>0.845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3444</v>
+        <v>0.0982</v>
       </c>
       <c r="V2" t="n">
         <v>0.0011</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7761</v>
+        <v>3.1257</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2709</v>
+        <v>3.4236</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4948</v>
+        <v>-0.2978</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1179</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7528</v>
+        <v>-0.4032</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1604</v>
+        <v>0.3131</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9133</v>
+        <v>-0.7163</v>
       </c>
       <c r="V3" t="n">
         <v>4.091</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0286</v>
+        <v>0.6604</v>
       </c>
       <c r="E4" t="n">
-        <v>0.903</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1256</v>
+        <v>-0.0468</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0174</v>
@@ -766,13 +766,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4345</v>
+        <v>1.0663</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9227</v>
+        <v>0.7269</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5118</v>
+        <v>0.3395</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9444</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GIL VARGAS</t>
+          <t>R. ROMERO NARANJO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3722</v>
+        <v>0.3837</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1029</v>
+        <v>1.0213</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4751</v>
+        <v>-0.6377</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036</v>
+        <v>-0.1525</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6888</v>
+        <v>-2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6529</v>
+        <v>2.0875</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3348</v>
+        <v>1.6481</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9877</v>
+        <v>-1.0997</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6529</v>
+        <v>2.7478</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2989</v>
+        <v>-1.8005</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2989</v>
+        <v>-1.1403</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.6603</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5215</v>
+        <v>0.1094</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4887</v>
+        <v>0.2997</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0328</v>
+        <v>-0.1903</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>G. GIL VARGAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1305</v>
+        <v>0.0298</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2264</v>
+        <v>-0.4946</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3569</v>
+        <v>0.5244</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9124</v>
+        <v>0.036</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6099</v>
+        <v>0.6888</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3024</v>
+        <v>-0.6529</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2548</v>
+        <v>0.3348</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1979</v>
+        <v>0.9877</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0569</v>
+        <v>-0.6529</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6575</v>
+        <v>-0.2989</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.412</v>
+        <v>-0.2989</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2456</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3012</v>
+        <v>0.1791</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0284</v>
+        <v>0.097</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7272</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. ROMERO NARANJO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.0631</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1538</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5392</v>
+        <v>0.7509</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1525</v>
+        <v>-1.9124</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.24</v>
+        <v>-0.6099</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0875</v>
+        <v>-1.3024</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6481</v>
+        <v>-1.2548</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0997</v>
+        <v>-0.1979</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7478</v>
+        <v>-1.0569</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8005</v>
+        <v>-0.6575</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1403</v>
+        <v>-0.412</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6603</v>
+        <v>-0.2456</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9671999999999999</v>
+        <v>0.1076</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8754</v>
+        <v>0.4409</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.3333</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9515</v>
+        <v>-0.9774</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9619</v>
+        <v>-1.2644</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9134</v>
+        <v>0.287</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.638</v>
+        <v>-1.1944</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7733</v>
+        <v>-1.0823</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8647</v>
+        <v>-0.1121</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8688</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4647</v>
+        <v>-0.6529</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.404</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7693</v>
+        <v>-0.583</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3085</v>
+        <v>-0.4294</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4607</v>
+        <v>-0.1536</v>
       </c>
       <c r="P9" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3895</v>
+        <v>-0.1536</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4983</v>
+        <v>-0.023</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1087</v>
+        <v>-0.1306</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1732</v>
+        <v>-1.6781</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4602</v>
+        <v>-0.6976</v>
       </c>
       <c r="F10" t="n">
-        <v>0.287</v>
+        <v>-0.9805</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1944</v>
+        <v>-0.9302</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0823</v>
+        <v>-0.9302</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1121</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.6314</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6529</v>
+        <v>-0.6314</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.583</v>
+        <v>-0.2989</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4294</v>
+        <v>-0.2989</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1536</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3494</v>
+        <v>0.0843</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2189</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1306</v>
+        <v>0.1505</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.63</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7022</v>
+        <v>-1.9723</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7955</v>
+        <v>-0.3544</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9067</v>
+        <v>-1.6179</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9302</v>
+        <v>-3.638</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9302</v>
+        <v>-2.7733</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.8647</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6314</v>
+        <v>-1.8688</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6314</v>
+        <v>-1.4647</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.404</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2989</v>
+        <v>-1.7693</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2989</v>
+        <v>-1.3085</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.4607</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7411</v>
+        <v>1.297</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0602</v>
+        <v>0.3687</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1641</v>
+        <v>1.182</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2243</v>
+        <v>-0.8133</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2086</v>
+        <v>-2.3497</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8090000000000001</v>
+        <v>-0.9502</v>
       </c>
       <c r="F12" t="n">
         <v>-1.3995</v>
@@ -1390,10 +1390,10 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0211</v>
+        <v>-0.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9227</v>
+        <v>0.7816</v>
       </c>
       <c r="U12" t="n">
         <v>-0.9016</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2666</v>
+        <v>-2.5275</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7717</v>
+        <v>-2.8356</v>
       </c>
       <c r="F13" t="n">
-        <v>0.505</v>
+        <v>0.308</v>
       </c>
       <c r="G13" t="n">
         <v>0.6753</v>
@@ -1468,13 +1468,13 @@
         <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2917</v>
+        <v>0.4474</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0037</v>
+        <v>0.9324</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.288</v>
+        <v>-0.485</v>
       </c>
       <c r="V13" t="n">
         <v>-0.315</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.124</v>
+        <v>-5.1191</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.6132</v>
+        <v>-5.4605</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4891</v>
+        <v>0.3414</v>
       </c>
       <c r="G14" t="n">
         <v>-4.078</v>
@@ -1546,13 +1546,13 @@
         <v>1.4823</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2509</v>
+        <v>0.2559</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3246</v>
+        <v>0.4772</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0736</v>
+        <v>-0.2214</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.781399999999998</v>
+        <v>-1.507700000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3641999999999985</v>
+        <v>0.6378000000000004</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1458</v>
+        <v>-2.1456</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.0228</v>
+        <v>-5.022799999999999</v>
       </c>
       <c r="H15" t="n">
         <v>-9.937900000000001</v>
@@ -1597,13 +1597,13 @@
         <v>4.915</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1248</v>
+        <v>4.124799999999999</v>
       </c>
       <c r="K15" t="n">
         <v>-2.7858</v>
       </c>
       <c r="L15" t="n">
-        <v>6.910599999999999</v>
+        <v>6.9106</v>
       </c>
       <c r="M15" t="n">
         <v>-9.1478</v>
@@ -1624,10 +1624,10 @@
         <v>13.8964</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6114</v>
+        <v>2.8851</v>
       </c>
       <c r="T15" t="n">
-        <v>5.7328</v>
+        <v>6.0066</v>
       </c>
       <c r="U15" t="n">
         <v>-3.1215</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9528</v>
+        <v>4.4425</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5731</v>
+        <v>3.0627</v>
       </c>
       <c r="F16" t="n">
         <v>1.3798</v>
@@ -1702,10 +1702,10 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9563</v>
+        <v>-0.4666</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.383</v>
+        <v>0.1066</v>
       </c>
       <c r="U16" t="n">
         <v>-0.5733</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3464</v>
+        <v>3.6173</v>
       </c>
       <c r="E17" t="n">
         <v>3.091</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2555</v>
+        <v>0.5263</v>
       </c>
       <c r="G17" t="n">
         <v>2.7121</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6066</v>
+        <v>-0.3358</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6029</v>
+        <v>-0.332</v>
       </c>
       <c r="V17" t="n">
         <v>0.3144</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2741</v>
+        <v>1.6115</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5051</v>
+        <v>2.1134</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.231</v>
+        <v>-0.5018</v>
       </c>
       <c r="G18" t="n">
         <v>3.7242</v>
@@ -1858,13 +1858,13 @@
         <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4213</v>
+        <v>-0.2413</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8133</v>
+        <v>0.4216</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.392</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.945</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3947</v>
+        <v>0.9061</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5715</v>
+        <v>0.8859</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1768</v>
+        <v>0.0202</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0842</v>
@@ -1936,13 +1936,13 @@
         <v>2.594</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4435</v>
+        <v>-0.0451</v>
       </c>
       <c r="T19" t="n">
-        <v>1.736</v>
+        <v>1.0505</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2925</v>
+        <v>-1.0956</v>
       </c>
       <c r="V19" t="n">
         <v>4.406</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1784</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0629</v>
+        <v>-0.1815</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8845</v>
+        <v>1.0076</v>
       </c>
       <c r="G20" t="n">
         <v>0.7655999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7037</v>
+        <v>-0.6992</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5471</v>
+        <v>0.3342</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1565</v>
+        <v>-1.0334</v>
       </c>
       <c r="V20" t="n">
         <v>0.945</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6966</v>
+        <v>-0.574</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6017</v>
+        <v>-0.5038</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0949</v>
+        <v>-0.0702</v>
       </c>
       <c r="G21" t="n">
         <v>-0.193</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.43</v>
+        <v>-0.3075</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0547</v>
+        <v>0.0432</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3753</v>
+        <v>-0.3507</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6294</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9527</v>
+        <v>-1.1194</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2418</v>
+        <v>-1.3934</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2891</v>
+        <v>0.274</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2827</v>
+        <v>-0.1535</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1596</v>
+        <v>0.4271</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4422</v>
+        <v>-0.5806</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4447</v>
+        <v>0.0282</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4033</v>
+        <v>-0.159</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>0.1872</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7274</v>
+        <v>-0.1817</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2437</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4837</v>
+        <v>-0.7678</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6676</v>
+        <v>0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9646</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9976</v>
+        <v>-1.1518</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6491</v>
+        <v>-0.4952</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3484</v>
+        <v>-0.6566</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8799</v>
+        <v>-1.4681</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8831</v>
+        <v>-1.5356</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0031</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1535</v>
+        <v>-0.2827</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4271</v>
+        <v>0.1596</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5806</v>
+        <v>-0.4422</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0282</v>
+        <v>0.4447</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.159</v>
+        <v>0.4033</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1872</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1817</v>
+        <v>-0.7274</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5862000000000001</v>
+        <v>-0.2437</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7678</v>
+        <v>-0.4837</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1853</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>-2.9646</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9123</v>
+        <v>0.4822</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9849</v>
+        <v>0.3554</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9274</v>
+        <v>0.1268</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0005</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0344</v>
+        <v>-2.3791</v>
       </c>
       <c r="E24" t="n">
         <v>-1.3779</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6565</v>
+        <v>-1.0012</v>
       </c>
       <c r="G24" t="n">
         <v>-0.44</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1502</v>
+        <v>-0.4949</v>
       </c>
       <c r="T24" t="n">
         <v>0.2114</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3617</v>
+        <v>-0.7064</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2589</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4446</v>
+        <v>-4.0814</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4274</v>
+        <v>-2.015</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0172</v>
+        <v>-2.0665</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6378</v>
@@ -2404,13 +2404,13 @@
         <v>1.4823</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2853</v>
+        <v>0.6485</v>
       </c>
       <c r="T25" t="n">
-        <v>1.685</v>
+        <v>1.0974</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3997</v>
+        <v>-0.4489</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4627</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.781400000000001</v>
+        <v>1.781499999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.1459</v>
+        <v>2.1458</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3643999999999998</v>
+        <v>-0.3642000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>5.0228</v>
@@ -2482,7 +2482,7 @@
         <v>13.8965</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6114</v>
+        <v>-2.6115</v>
       </c>
       <c r="T26" t="n">
         <v>3.1214</v>
